--- a/excel/passiveskill.xlsx
+++ b/excel/passiveskill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79724086-FBDE-4B6F-8737-D8229C08307B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6AB821-2D43-42F5-A784-2A76F1E9B9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1080" windowWidth="19966" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27555" yWindow="653" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -146,18 +146,6 @@
     <t>res://Art/Icon/pskill204.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>你每消耗5具尸体，获得1次祭坛奖励</t>
-    </r>
-  </si>
-  <si>
     <t>尸横遍野</t>
   </si>
   <si>
@@ -177,6 +165,70 @@
   </si>
   <si>
     <t>战斗胜利后，触发1次尸体事件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>涌流</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill206.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>法力值上限+5，移动后获得1点法力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>摘取</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill207.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动到与草地相邻的位置时，自动触发该草地的效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>食尸鬼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill103.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入尸体变为快速行动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill106.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你每消耗5具尸体，获得1次祭坛奖励</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草食动物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>草丛恢复生命值的概率变为100%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小跳</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill208.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的移动范围扩大1格</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="33.796875" customWidth="1"/>
@@ -556,33 +608,30 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -590,84 +639,163 @@
     </row>
     <row r="6" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="E10">
+    </row>
+    <row r="11" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>204</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>205</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12">
         <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>206</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>207</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>208</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/excel/passiveskill.xlsx
+++ b/excel/passiveskill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6AB821-2D43-42F5-A784-2A76F1E9B9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF2F461-776F-4195-8B38-62CE38A190DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27555" yWindow="653" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20970" yWindow="840" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>ID</t>
   </si>
@@ -50,9 +50,6 @@
     <t>res://Art/Icon/pskill101.png</t>
   </si>
   <si>
-    <t>进入草地变为快速行动</t>
-  </si>
-  <si>
     <t>生机蔓延</t>
   </si>
   <si>
@@ -66,18 +63,6 @@
   </si>
   <si>
     <t>res://Art/Icon/pskill104.png</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>每进入2次草地，下一次探索变为快速行动</t>
-    </r>
   </si>
   <si>
     <t>草叶精华</t>
@@ -104,36 +89,12 @@
     <t>res://Art/Icon/pskill201.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>尸体触发恢复生命值时，额外恢复1点</t>
-    </r>
-  </si>
-  <si>
     <t>因果轮回</t>
   </si>
   <si>
     <t>res://Art/Icon/pskill202.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>你因尸体而失去生命时，下一次战斗获胜后恢复1点生命</t>
-    </r>
-  </si>
-  <si>
     <t>葬仪</t>
   </si>
   <si>
@@ -152,22 +113,6 @@
     <t>res://Art/Icon/pskill205.png</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>每次BOSS使用技能后，在范围内留下2具尸体</t>
-    </r>
-  </si>
-  <si>
-    <t>战斗胜利后，触发1次尸体事件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>涌流</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -188,10 +133,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>移动到与草地相邻的位置时，自动触发该草地的效果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>食尸鬼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -200,18 +141,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>进入尸体变为快速行动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>res://Art/Icon/pskill106.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>你每消耗5具尸体，获得1次祭坛奖励</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>草食动物</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -230,6 +163,57 @@
   <si>
     <t>你的移动范围扩大1格</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>滚石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill107.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的移动可以无视并摧毁障碍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力药草</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Art/Icon/pskill108.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你每触发6次草丛，提升1点魔法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入墓地变为快速行动</t>
+  </si>
+  <si>
+    <t>墓地触发恢复生命值时，额外恢复1点</t>
+  </si>
+  <si>
+    <t>你因墓地而失去生命时，下一次战斗获胜后恢复1点生命</t>
+  </si>
+  <si>
+    <t>每2次战斗胜利后，触发1次墓地事件</t>
+  </si>
+  <si>
+    <t>你每触发6次墓地，提升1点力量</t>
+  </si>
+  <si>
+    <t>每次BOSS使用技能后，在范围内留下1具墓地</t>
+  </si>
+  <si>
+    <t>进入草丛变为快速行动</t>
+  </si>
+  <si>
+    <t>每次进入草丛后，下一次探索变为快速行动</t>
+  </si>
+  <si>
+    <t>移动到与草丛相邻的位置时，自动触发该草丛的效果</t>
   </si>
 </sst>
 </file>
@@ -551,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="33.796875" customWidth="1"/>
@@ -586,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
@@ -594,13 +578,13 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -611,13 +595,13 @@
         <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
@@ -625,13 +609,13 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -642,13 +626,13 @@
         <v>105</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -659,109 +643,103 @@
         <v>106</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E13">
         <v>5</v>
@@ -769,32 +747,66 @@
     </row>
     <row r="14" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>49</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A15">
+        <v>206</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>207</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
+      <c r="A17">
         <v>208</v>
       </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
     </row>
